--- a/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-woodland/results/SoIB_summaries.xlsx
@@ -506,13 +506,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -526,13 +526,13 @@
         <v>38</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>33.6</v>
+        <v>33.3</v>
       </c>
       <c r="E3">
-        <v>16.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -546,10 +546,10 @@
         <v>103</v>
       </c>
       <c r="D4">
-        <v>25.7</v>
+        <v>25.4</v>
       </c>
       <c r="E4">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,10 +563,10 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="E5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -591,10 +591,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C7">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -602,10 +602,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C8">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -708,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -716,7 +716,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +745,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,10 +753,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C3">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -764,10 +764,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C4">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -810,16 +810,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2">
-        <v>64.2</v>
+        <v>64.5</v>
       </c>
       <c r="D2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -830,13 +830,13 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -847,7 +847,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>32.1</v>
+        <v>31.8</v>
       </c>
       <c r="D4">
         <v>2</v>
